--- a/reports/security/findings.xlsx
+++ b/reports/security/findings.xlsx
@@ -561,7 +561,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 08:15 UTC | Total Findings: 62</t>
+          <t>Generated: 2026-06-23 09:15 UTC | Total Findings: 62</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>generic-api-key</t>
+          <t>jwt</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>352241</t>
+          <t>353515</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Generic API Key</t>
+          <t>JSON Web Token</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>generic-api-key</t>
+          <t>jwt</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>354388</t>
+          <t>354360</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Generic API Key</t>
+          <t>JSON Web Token</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>generic-api-key</t>
+          <t>private-key</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>354471</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Generic API Key</t>
+          <t>Private Key</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>354471</t>
+          <t>352241</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>generic-api-key</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>353515</t>
+          <t>354388</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>JSON Web Token</t>
+          <t>Generic API Key</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>generic-api-key</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>354360</t>
+          <t>354471</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>JSON Web Token</t>
+          <t>Generic API Key</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>aws-access-token</t>
+          <t>generic-api-key</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>347129</t>
+          <t>354471</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Generic API Key</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>348359</t>
+          <t>347129</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>349074</t>
+          <t>348359</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>349705</t>
+          <t>349074</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>350272</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>352978</t>
+          <t>350272</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>354310</t>
+          <t>352978</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>354389</t>
+          <t>354310</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>356295</t>
+          <t>354389</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>356310</t>
+          <t>356295</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>356778</t>
+          <t>356310</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>356779</t>
+          <t>356778</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>private-key</t>
+          <t>aws-access-token</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>356779</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Private Key</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
